--- a/KEIKI_SofaBed_新标题.xlsx
+++ b/KEIKI_SofaBed_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout Comfy Lounge Black</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout USB Cup Holders Comfy Lounge Black</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout Comfy Lounge Grey</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout USB Cup Holders Comfy Lounge Grey</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout Comfy Lounge Orange</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout USB Cup Holders Comfy Lounge Orange</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout Comfy Lounge White</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout USB Cup Holders Comfy Lounge White</t>
         </is>
       </c>
     </row>

--- a/KEIKI_SofaBed_新标题.xlsx
+++ b/KEIKI_SofaBed_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout USB Cup Holders Comfy Lounge Black</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing ...</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout USB Cup Holders Comfy Lounge Grey</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing ...</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout USB Cup Holders Comfy Lounge Orange</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing ...</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible for Living Room Flexible Layout USB Cup Holders Comfy Lounge White</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing ...</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Orange</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Orange</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Blue</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Blue</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Black</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Green</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Green</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Yellow</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Yellow</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Grey</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Grey</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Beige</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Beige</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Light Camel</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Light Camel</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Speckled Black</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Speckled Black</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Moss Green</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Moss Green</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Ochre</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Ochre</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Black</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Black</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Dark Gray</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Azure</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Azure</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Comfy Lounge Blue</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Suppo...</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Comfy Lounge Brown</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Suppo...</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Comfy Lounge Green</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Suppo...</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Comfy Lounge Grayish Green</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Grayish Green</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Orange</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Orange</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Light Gray</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Light Gray</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Comfy Lounge Beige</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Beige</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Dark Gray</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Azure</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Azure</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Blue</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Brown</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Brown</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Grayish Green</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Grayis...</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Green</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Orange</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Orange</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Gray</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Light ...</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Beige</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Flexible Layout Comfy Lounge Black</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Black</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Velvet Sofa Couch for Living Room Comfy Lounge Black</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Su...</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Velvet Sofa Couch for Living Room Comfy Lounge White</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Su...</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Velvet Sofa Couch for Living Room Comfy Lounge Dark Gray</t>
+          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Su...</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Velvet Sofa Couch Storage for Living Room Comfy Lounge Gray</t>
+          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Gray</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Velvet Sofa Couch Storage for Living Room Comfy Lounge Black</t>
+          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Black</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Velvet Sofa Couch Storage for Living Room Comfy Lounge Beige</t>
+          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Beige</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Velvet Sofa Couch Storage for Living Room Comfy Lounge Pink</t>
+          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Pink</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Velvet Sofa Couch Storage for Living Room Comfy Lounge Brown</t>
+          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Brown</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Velvet Sofa Couch Storage for Living Room Comfy Lounge Cyan</t>
+          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Cyan</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Velvet Sofa Couch Storage for Living Room Comfy Lounge Blue</t>
+          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Blue</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Comfy Lounge Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive ...</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Comfy Lounge Green</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive ...</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Comfy Lounge Black</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive ...</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Comfy Lounge Beige</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive ...</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Comfy Lounge Gray</t>
+          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Gray</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Comfy Lounge Blue</t>
+          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Blue</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Comfy Lounge Black</t>
+          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Black</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Comfy Lounge Pink</t>
+          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Pink</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Comfy Lounge Beige</t>
+          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Beige</t>
         </is>
       </c>
     </row>

--- a/KEIKI_SofaBed_新标题.xlsx
+++ b/KEIKI_SofaBed_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing ...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Office Flexible Layout Soft Plush Comfortable Lou...</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing ...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Office Flexible Layout Soft Plush Comfortable Lou...</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing ...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Office Flexible Layout Soft Plush Comfortable Lou...</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing ...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Office Flexible Layout Soft Plush Comfortable Lou...</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Orange</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Blue</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Black</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Green</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Yellow</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Grey</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Beige</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Light Camel</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Speckled Black</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Moss Green</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Ochre</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Black</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Dark Gray</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Azure</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Suppo...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Suppo...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Brown</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Suppo...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Grayish Green</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Gr...</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Orange</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Light Gray</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Beige</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Dark Gray</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Azure</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Blue</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Brown</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Grayis...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Green</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Orange</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Light ...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Beige</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Black</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Su...</t>
+          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Desig...</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Su...</t>
+          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Desig...</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Su...</t>
+          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Desig...</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Gray</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Black</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Beige</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Pink</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Brown</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Cyan</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Blue</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive ...</t>
+          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cush...</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive ...</t>
+          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cush...</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive ...</t>
+          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cush...</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Convertible Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive ...</t>
+          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cush...</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Gray</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam...</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Blue</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam...</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Black</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Pink</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam...</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Sectional Convertible Velvet Sofa Couch with Chaise for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Beige</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige</t>
         </is>
       </c>
     </row>

--- a/KEIKI_SofaBed_新标题.xlsx
+++ b/KEIKI_SofaBed_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Office Flexible Layout Soft Plush Comfortable Lou...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Urban Loft Apartment Living Flexible Layout Sleek Bold Perfect for...</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Office Flexible Layout Soft Plush Comfortable Lou...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for City Apartment Small Space Adjustable Configuration Neutral Calm I...</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Office Flexible Layout Soft Plush Comfortable Lou...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Creative Studio Bedroom Studio Versatile Arrangement Energetic Vib...</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Living Room Home Office Flexible Layout Soft Plush Comfortable Lou...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Modern Home Home Office Customizable Setup Clean Bright Designed f...</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Creative Studio Apartment Living Flexible Layout Deep Seat Energetic Vibrant Perfect for Relaxing Lounge Space Eclectic Design Orange</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Coastal Home Small Space Adjustable Configuration Plush Cushions Serene Peaceful Ideal for Entertaining Lounge Space Hamptons Design ...</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Urban Loft Bedroom Studio Versatile Arrangement Spacious Design Sleek Bold Great for Lounging Lounge Space Contemporary Design Black</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Garden Home Home Office Customizable Setup Comfy Support Fresh Natural Designed for Comfort Lounge Space Organic Design Green</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Sunny Apartment Apartment Living Flexible Layout Deep Seat Happy Optimistic Perfect for Relaxing Lounge Space Mid Century Design Yellow</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for City Apartment Small Space Adjustable Configuration Plush Cushions Neutral Calm Ideal for Entertaining Lounge Space Modern Design Grey</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Cozy Cottage Bedroom Studio Versatile Arrangement Spacious Design Warm Inviting Great for Lounging Lounge Space Traditional Design Beige</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for California Casual Home Office Customizable Setup Sunny Relaxed Designed for Comfort Lounge Space Coastal Design Light Camel</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design Speckled Black</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Forest Retreat Small Space Adjustable Configuration Lush Restorative Ideal for Entertaining Lounge Space Botanical Design Moss Green</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design Ochre</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable ...</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Executive Suite Apartment Living Flexible Layout Professional Refined Perfect for Relaxing Lounge Space Luxury Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Beach House Small Space Adjustable Configuration Crisp Refreshing Ideal for Entertaining Lounge Space Nautical Design Azure</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Su...</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Brown</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Rustic Home Home Office Customizable Setup Earthy Classic Designed for Comfort Lounge Space Vintage Design High Quality Comfortable Supportiv...</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Garden Home Apartment Living Flexible Layout Fresh Natural Perfect for Relaxing Lounge Space Organic Design High Quality Comfortable Supporti...</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Gr...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Sage Sanctuary Small Space Adjustable Configuration Soothing Harmonious Ideal for Entertaining Lounge Space Japandi Design Grayish Green</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Creative Studio Bedroom Studio Versatile Arrangement Energetic Vibrant Great for Lounging Lounge Space Eclectic Design Orange</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design Light Gray</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Modern ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Cozy Cottage Apartment Living Flexible Layout Warm Inviting Perfect for Relaxing Lounge Space Traditional Design High Quality Comfor...</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Executive Suite Small Space Adjustable Configuration Professional Refined Ideal for Entertaining Lounge Space Luxury Desi...</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Beach House Bedroom Studio Versatile Arrangement Crisp Refreshing Great for Lounging Lounge Space Nautical Design Azure</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Coastal Home Home Office Customizable Setup Serene Peaceful Designed for Comfort Lounge Space Hamptons Design Blue</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Rustic Home Apartment Living Flexible Layout Earthy Classic Perfect for Relaxing Lounge Space Vintage Design Brown</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Sage Sanctuary Small Space Adjustable Configuration Soothing Harmonious Ideal for Entertaining Lounge Space Japandi Desig...</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Design Green</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Creative Studio Home Office Customizable Setup Energetic Vibrant Designed for Comfort Lounge Space Eclectic Design Orange</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design L...</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Cozy Cottage Small Space Adjustable Configuration Warm Inviting Ideal for Entertaining Lounge Space Traditional Design Beige</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Living Room Bedroom Apartment Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assem...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Urban Loft Bedroom Studio Versatile Arrangement Sleek Bold Great for Lounging Lounge Space Contemporary Design Black</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Desig...</t>
+          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Sup...</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Desig...</t>
+          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Modern Home Apartment Living Flexible Layout Clean Bright Perfect for Relaxing Lounge Space Minimalist Design High Quality Comfortable ...</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Desig...</t>
+          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Executive Suite Small Space Adjustable Configuration Professional Refined Ideal for Entertaining Lounge Space Luxury Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for City Apartment Bedroom Studio Versatile Arrangement Neutral Calm Great for Lounging Lounge Space Modern Design High Quality Comfor...</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortabl...</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Cozy Cottage Apartment Living Flexible Layout Warm Inviting Perfect for Relaxing Lounge Space Traditional Design Beige</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Feminine Retreat Small Space Adjustable Configuration Romantic Dreamy Ideal for Entertaining Lounge Space Glam Design Pink</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Rustic Home Bedroom Studio Versatile Arrangement Earthy Classic Great for Lounging Lounge Space Vintage Design High Quality Comfor...</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design Cyan</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly M...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Coastal Home Apartment Living Flexible Layout Serene Peaceful Perfect for Relaxing Lounge Space Hamptons Design High Quality Comfo...</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cush...</t>
+          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Coastal Home Small Space Adjustable Configuration Serene Peaceful Ideal for Entertaining Lounge Space Hamptons Design High Quality Comfortable Suppor...</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cush...</t>
+          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Design High Quality Comfortable Supportive Ele...</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cush...</t>
+          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Supportive Elegan...</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cush...</t>
+          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Cozy Cottage Apartment Living Flexible Layout Warm Inviting Perfect for Relaxing Lounge Space Traditional Design High Quality Comfortable Supportive ...</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam...</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for City Apartment Small Space Adjustable Configuration Neutral Calm Ideal for Entertaining Lounge Space Modern Design High Quality Comfortable Supportive Ele...</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam...</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Supportive Eleg...</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Supportive Elegant Black</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam...</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Feminine Retreat Apartment Living Flexible Layout Romantic Dreamy Perfect for Relaxing Lounge Space Glam Design High Quality Comfortable Supportive Elegan...</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Cozy Cottage Small Space Adjustable Configuration Warm Inviting Ideal for Entertaining Lounge Space Traditional Design High Quality Comfortable Supportive...</t>
         </is>
       </c>
     </row>

--- a/KEIKI_SofaBed_新标题.xlsx
+++ b/KEIKI_SofaBed_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Urban Loft Apartment Living Flexible Layout Sleek Bold Perfect for...</t>
+          <t>KEIKI 83" 4Seat Modular Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Industrial Loft Family Living Room Family Friendly Urban Professionals Adapt...</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for City Apartment Small Space Adjustable Configuration Neutral Calm I...</t>
+          <t>KEIKI 83" 4Seat Modular Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for City Apartment Family Living Room Family Friendly Practical Buyers Adaptable...</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Creative Studio Bedroom Studio Versatile Arrangement Energetic Vib...</t>
+          <t>KEIKI 83" 4Seat Modular Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Artistic Studio Family Living Room Family Friendly Creative Types Adaptable ...</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Modern Home Home Office Customizable Setup Clean Bright Designed f...</t>
+          <t>KEIKI 83" 4Seat Modular Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Bright Modern Home Family Living Room Family Friendly Minimalists Adaptable ...</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Creative Studio Apartment Living Flexible Layout Deep Seat Energetic Vibrant Perfect for Relaxing Lounge Space Eclectic Design Orange</t>
+          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Artistic Studio Family Living Room Family Friendly Creative Types Adaptable Homeowners Warm Textured Perfect for Energetic Creative Relaxation ...</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Coastal Home Small Space Adjustable Configuration Plush Cushions Serene Peaceful Ideal for Entertaining Lounge Space Hamptons Design ...</t>
+          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Coastal Home Family Living Room Family Friendly Beach Lovers Adaptable Homeowners Warm Textured Ideal for Warm Textured Lounging Rustic Farmhou...</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Urban Loft Bedroom Studio Versatile Arrangement Spacious Design Sleek Bold Great for Lounging Lounge Space Contemporary Design Black</t>
+          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Industrial Loft Family Living Room Family Friendly Urban Professionals Adaptable Homeowners Warm Textured Great for Comfortable Gathering Space...</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Garden Home Home Office Customizable Setup Comfy Support Fresh Natural Designed for Comfort Lounge Space Organic Design Green</t>
+          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Garden Oasis Family Living Room Family Friendly Plant Parents Adaptable Homeowners Warm Textured Designed for Flexible Configuration Rustic Far...</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Sunny Apartment Apartment Living Flexible Layout Deep Seat Happy Optimistic Perfect for Relaxing Lounge Space Mid Century Design Yellow</t>
+          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Modern Home Family Living Room Family Friendly Homeowners Adaptable Homeowners Warm Textured Perfect for Comfortable Relaxation Rustic Farmhous...</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for City Apartment Small Space Adjustable Configuration Plush Cushions Neutral Calm Ideal for Entertaining Lounge Space Modern Design Grey</t>
+          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for City Apartment Family Living Room Family Friendly Practical Buyers Adaptable Homeowners Warm Textured Ideal for Warm Textured Lounging Rustic F...</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Cozy Cottage Bedroom Studio Versatile Arrangement Spacious Design Warm Inviting Great for Lounging Lounge Space Traditional Design Beige</t>
+          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Cozy Cottage Family Living Room Family Friendly Traditional Families Adaptable Homeowners Warm Textured Great for Comfortable Gathering Space R...</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for California Casual Home Office Customizable Setup Sunny Relaxed Designed for Comfort Lounge Space Coastal Design Light Camel</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for California Casual Compact Studio Family Friendly West Coast Style Practical Buyers Warm Textured Designed for Versa...</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design Speckled Black</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Modern Home Compact Studio Family Friendly Homeowners Practical Buyers Warm Textured Perfect for Comfortable Relaxa...</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Forest Retreat Small Space Adjustable Configuration Lush Restorative Ideal for Entertaining Lounge Space Botanical Design Moss Green</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Forest Retreat Compact Studio Family Friendly Wellness Focused Practical Buyers Warm Textured Ideal for Warm Textur...</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design Ochre</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Modern Home Compact Studio Family Friendly Homeowners Practical Buyers Warm Textured Great for Intimate Cozy Corner...</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable ...</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Industrial Loft Compact Studio Family Friendly Urban Professionals Practical Buyers Warm Textured Designed for Vers...</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Executive Suite Apartment Living Flexible Layout Professional Refined Perfect for Relaxing Lounge Space Luxury Design Dark Gray</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Executive Suite Compact Studio Family Friendly Luxury Buyers Practical Buyers Warm Textured Perfect for Professiona...</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Beach House Small Space Adjustable Configuration Crisp Refreshing Ideal for Entertaining Lounge Space Nautical Design Azure</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Beach House Compact Studio Family Friendly Nautical Fans Practical Buyers Warm Textured Ideal for Warm Textured Lou...</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Su...</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Practical Buyers Luxuriously Soft Great for Intimate Cozy Co...</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Rustic Home Home Office Customizable Setup Earthy Classic Designed for Comfort Lounge Space Vintage Design High Quality Comfortable Supportiv...</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Velvet Loveseat Sofa Couch for Rustic Home Compact Studio Style Conscious Nature Lovers Practical Buyers Luxuriously Soft Designed for Versatile Lay...</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Garden Home Apartment Living Flexible Layout Fresh Natural Perfect for Relaxing Lounge Space Organic Design High Quality Comfortable Supporti...</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Practical Buyers Luxuriously Soft Perfect for Fresh Natural...</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Sofa Couch for Sage Sanctuary Small Space Adjustable Configuration Soothing Harmonious Ideal for Entertaining Lounge Space Japandi Design Grayish Green</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lo...</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Creative Studio Bedroom Studio Versatile Arrangement Energetic Vibrant Great for Lounging Lounge Space Eclectic Design Orange</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Artistic Studio Compact Studio Family Friendly Creative Types Practical Buyers Warm Textured Great for Intimate Coz...</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design Light Gray</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Modern Home Compact Studio Family Friendly Homeowners Practical Buyers Warm Textured Designed for Versatile Layout ...</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Sleeper Convertible Corduroy Sofa Couch for Cozy Cottage Apartment Living Flexible Layout Warm Inviting Perfect for Relaxing Lounge Space Traditional Design High Quality Comfor...</t>
+          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Cozy Cottage Compact Studio Family Friendly Traditional Families Practical Buyers Warm Textured Perfect for Warm In...</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Executive Suite Small Space Adjustable Configuration Professional Refined Ideal for Entertaining Lounge Space Luxury Desi...</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Executive Suite Family Living Room Family Friendly Luxury Buyers Adaptable Homeowners Warm Textured Ideal for Warm Textured Loungin...</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Beach House Bedroom Studio Versatile Arrangement Crisp Refreshing Great for Lounging Lounge Space Nautical Design Azure</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Beach House Family Living Room Family Friendly Nautical Fans Adaptable Homeowners Warm Textured Great for Comfortable Gathering Spa...</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Coastal Home Home Office Customizable Setup Serene Peaceful Designed for Comfort Lounge Space Hamptons Design Blue</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Coastal Home Family Living Room Family Friendly Beach Lovers Adaptable Homeowners Warm Textured Designed for Flexible Configuration...</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Rustic Home Apartment Living Flexible Layout Earthy Classic Perfect for Relaxing Lounge Space Vintage Design Brown</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Rustic Home Family Living Room Family Friendly Nature Lovers Adaptable Homeowners Warm Textured Perfect for Grounded Natural Relaxa...</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Sage Sanctuary Small Space Adjustable Configuration Soothing Harmonious Ideal for Entertaining Lounge Space Japandi Desig...</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Modern Home Family Living Room Family Friendly Homeowners Adaptable Homeowners Warm Textured Ideal for Warm Textured Lounging Rusti...</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Design Green</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Garden Oasis Family Living Room Family Friendly Plant Parents Adaptable Homeowners Warm Textured Great for Comfortable Gathering Sp...</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Creative Studio Home Office Customizable Setup Energetic Vibrant Designed for Comfort Lounge Space Eclectic Design Orange</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Artistic Studio Family Living Room Family Friendly Creative Types Adaptable Homeowners Warm Textured Designed for Flexible Configur...</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design L...</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Modern Home Family Living Room Family Friendly Homeowners Adaptable Homeowners Warm Textured Perfect for Comfortable Relaxation Rus...</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Cozy Cottage Small Space Adjustable Configuration Warm Inviting Ideal for Entertaining Lounge Space Traditional Design Beige</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Cozy Cottage Family Living Room Family Friendly Traditional Families Adaptable Homeowners Warm Textured Ideal for Warm Textured Lou...</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Sectional Convertible Corduroy Sofa Couch for Urban Loft Bedroom Studio Versatile Arrangement Sleek Bold Great for Lounging Lounge Space Contemporary Design Black</t>
+          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Industrial Loft Family Living Room Family Friendly Urban Professionals Adaptable Homeowners Warm Textured Great for Comfortable Gat...</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Sup...</t>
+          <t>KEIKI 78" 2Seat Modular Convertible Turtle Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Comfort Seekers Urban Professionals Practical Buyers Ultra Soft Plush Designed for Vers...</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Modern Home Apartment Living Flexible Layout Clean Bright Perfect for Relaxing Lounge Space Minimalist Design High Quality Comfortable ...</t>
+          <t>KEIKI 78" 2Seat Modular Convertible Turtle Velvet Loveseat Sofa Couch for Bright Modern Home Compact Studio Comfort Seekers Minimalists Practical Buyers Ultra Soft Plush Perfect for Clean Airy...</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Convertible Turtle Velvet Sofa Couch for Executive Suite Small Space Adjustable Configuration Professional Refined Ideal for Entertaining Lounge Space Luxury Design Dark Gray</t>
+          <t>KEIKI 78" 2Seat Modular Convertible Turtle Velvet Loveseat Sofa Couch for Executive Suite Compact Studio Comfort Seekers Luxury Buyers Practical Buyers Ultra Soft Plush Ideal for Ultra Soft Pl...</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for City Apartment Bedroom Studio Versatile Arrangement Neutral Calm Great for Lounging Lounge Space Modern Design High Quality Comfor...</t>
+          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Modern Home Compact Studio Comfort Seekers Homeowners Practical Buyers Ultra Soft Plush Great for Intimate Cozy Corner Contemporar...</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortabl...</t>
+          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Comfort Seekers Urban Professionals Practical Buyers Ultra Soft Plush Designed for Versatile Layout...</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Cozy Cottage Apartment Living Flexible Layout Warm Inviting Perfect for Relaxing Lounge Space Traditional Design Beige</t>
+          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Cozy Cottage Compact Studio Comfort Seekers Traditional Families Practical Buyers Ultra Soft Plush Perfect for Warm Inviting Relax...</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Feminine Retreat Small Space Adjustable Configuration Romantic Dreamy Ideal for Entertaining Lounge Space Glam Design Pink</t>
+          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Feminine Retreat Compact Studio Comfort Seekers Glam Seekers Practical Buyers Ultra Soft Plush Ideal for Ultra Soft Plush Lounging...</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Rustic Home Bedroom Studio Versatile Arrangement Earthy Classic Great for Lounging Lounge Space Vintage Design High Quality Comfor...</t>
+          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Rustic Home Compact Studio Comfort Seekers Nature Lovers Practical Buyers Ultra Soft Plush Great for Intimate Cozy Corner Contempo...</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design Cyan</t>
+          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Modern Home Compact Studio Comfort Seekers Homeowners Practical Buyers Ultra Soft Plush Designed for Versatile Layout Contemporary...</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch Storage for Coastal Home Apartment Living Flexible Layout Serene Peaceful Perfect for Relaxing Lounge Space Hamptons Design High Quality Comfo...</t>
+          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Comfort Seekers Beach Lovers Practical Buyers Ultra Soft Plush Perfect for Serene Peaceful Relaxation ...</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Coastal Home Small Space Adjustable Configuration Serene Peaceful Ideal for Entertaining Lounge Space Hamptons Design High Quality Comfortable Suppor...</t>
+          <t>KEIKI 76" 2Seat Modular Convertible Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Loungin...</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Design High Quality Comfortable Supportive Ele...</t>
+          <t>KEIKI 76" 2Seat Modular Convertible Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Practical Buyers Luxuriously Soft Great for Intimate Cozy Corner Gl...</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Supportive Elegan...</t>
+          <t>KEIKI 76" 2Seat Modular Convertible Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Designed for Versatile L...</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Convertible Sofa Couch for Cozy Cottage Apartment Living Flexible Layout Warm Inviting Perfect for Relaxing Lounge Space Traditional Design High Quality Comfortable Supportive ...</t>
+          <t>KEIKI 76" 2Seat Modular Convertible Velvet Loveseat Sofa Couch for Cozy Cottage Compact Studio Style Conscious Traditional Families Practical Buyers Luxuriously Soft Perfect for Warm Inviting ...</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for City Apartment Small Space Adjustable Configuration Neutral Calm Ideal for Entertaining Lounge Space Modern Design High Quality Comfortable Supportive Ele...</t>
+          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Gray</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Supportive Eleg...</t>
+          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Practical Buyers Luxuriously Soft Great for Intimate Cozy Corner Glam Modern Blue</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Supportive Elegant Black</t>
+          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Designed for Versatile Layout Glam M...</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Feminine Retreat Apartment Living Flexible Layout Romantic Dreamy Perfect for Relaxing Lounge Space Glam Design High Quality Comfortable Supportive Elegan...</t>
+          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Feminine Retreat Compact Studio Style Conscious Glam Seekers Practical Buyers Luxuriously Soft Perfect for Romantic Soft Relaxation Glam ...</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Cozy Cottage Small Space Adjustable Configuration Warm Inviting Ideal for Entertaining Lounge Space Traditional Design High Quality Comfortable Supportive...</t>
+          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Cozy Cottage Compact Studio Style Conscious Traditional Families Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lounging Gl...</t>
         </is>
       </c>
     </row>

--- a/KEIKI_SofaBed_新标题.xlsx
+++ b/KEIKI_SofaBed_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Industrial Loft Family Living Room Family Friendly Urban Professionals Adapt...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Urban Loft Apartment Living Family Friendly Contemporary Design Black</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for City Apartment Family Living Room Family Friendly Practical Buyers Adaptable...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for City Apartment Small Space Family Friendly Premium Design Grey</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Artistic Studio Family Living Room Family Friendly Creative Types Adaptable ...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Creative Studio Bedroom Studio Family Friendly Quality Design Orange</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 83" 4Seat Modular Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Bright Modern Home Family Living Room Family Friendly Minimalists Adaptable ...</t>
+          <t>KEIKI 83" 4Seat Modular Sectional Sleeper Pull Out Bed Corduroy Sofa Couch with Chaise Storage Reversible USB Cup Holders for Modern Home Home Office Family Friendly Refined Design White</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Artistic Studio Family Living Room Family Friendly Creative Types Adaptable Homeowners Warm Textured Perfect for Energetic Creative Relaxation ...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Creative Studio Apartment Living Family Friendly Creative Types Soft Plush Comfortable Cozy Relaxing Lounge Contemporary Design Orange</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Coastal Home Family Living Room Family Friendly Beach Lovers Adaptable Homeowners Warm Textured Ideal for Warm Textured Lounging Rustic Farmhou...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Coastal Home Small Space Family Friendly Beach Lovers Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Blue</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Industrial Loft Family Living Room Family Friendly Urban Professionals Adaptable Homeowners Warm Textured Great for Comfortable Gathering Space...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Urban Loft Bedroom Studio Family Friendly Urban Professionals Luxurious Elegant Sophisticated Refined Design Quality Design Black</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Garden Oasis Family Living Room Family Friendly Plant Parents Adaptable Homeowners Warm Textured Designed for Flexible Configuration Rustic Far...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Garden Home Home Office Family Friendly Nature Lovers Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Green</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Modern Home Family Living Room Family Friendly Homeowners Adaptable Homeowners Warm Textured Perfect for Comfortable Relaxation Rustic Farmhous...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Sunny Apartment Apartment Living Family Friendly Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Contemporary Design Yellow</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for City Apartment Family Living Room Family Friendly Practical Buyers Adaptable Homeowners Warm Textured Ideal for Warm Textured Lounging Rustic F...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for City Apartment Small Space Family Friendly Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Grey</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 108" 4Seat Modular Corduroy Sofa Couch for Cozy Cottage Family Living Room Family Friendly Traditional Families Adaptable Homeowners Warm Textured Great for Comfortable Gathering Space R...</t>
+          <t>KEIKI 108" 4Seat Modular Sectional Corduroy Sofa Couch for Cozy Cottage Bedroom Studio Family Friendly Traditional Families Luxurious Elegant Sophisticated Refined Design Quality Design Beige</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for California Casual Compact Studio Family Friendly West Coast Style Practical Buyers Warm Textured Designed for Versa...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Casual Home Home Office Family Friendly Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Light</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Modern Home Compact Studio Family Friendly Homeowners Practical Buyers Warm Textured Perfect for Comfortable Relaxa...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Living Room Apartment Living Family Friendly Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Speckled Black</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Forest Retreat Compact Studio Family Friendly Wellness Focused Practical Buyers Warm Textured Ideal for Warm Textur...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Forest Retreat Small Space Family Friendly Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Moss</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Modern Home Compact Studio Family Friendly Homeowners Practical Buyers Warm Textured Great for Intimate Cozy Corner...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Artistic Space Bedroom Studio Family Friendly Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Ochre</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Industrial Loft Compact Studio Family Friendly Urban Professionals Practical Buyers Warm Textured Designed for Vers...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Urban Loft Home Office Family Friendly Urban Professionals Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Black</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Executive Suite Compact Studio Family Friendly Luxury Buyers Practical Buyers Warm Textured Perfect for Professiona...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Executive Suite Apartment Living Family Friendly Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Beach House Compact Studio Family Friendly Nautical Fans Practical Buyers Warm Textured Ideal for Warm Textured Lou...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Beach House Small Space Family Friendly Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Azure</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Practical Buyers Luxuriously Soft Great for Intimate Cozy Co...</t>
+          <t>KEIKI 78" 2Seat Sleeper Velvet Sofa Couch for Coastal Home Bedroom Studio Style Conscious Beach Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Blue</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Velvet Loveseat Sofa Couch for Rustic Home Compact Studio Style Conscious Nature Lovers Practical Buyers Luxuriously Soft Designed for Versatile Lay...</t>
+          <t>KEIKI 78" 2Seat Sleeper Velvet Sofa Couch for Rustic Home Home Office Style Conscious Rustic Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Practical Buyers Luxuriously Soft Perfect for Fresh Natural...</t>
+          <t>KEIKI 78" 2Seat Sleeper Velvet Sofa Couch for Garden Home Apartment Living Style Conscious Nature Lovers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Green</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lo...</t>
+          <t>KEIKI 78" 2Seat Sleeper Velvet Sofa Couch for Zen Space Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Grayish Green</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Artistic Studio Compact Studio Family Friendly Creative Types Practical Buyers Warm Textured Great for Intimate Coz...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Creative Studio Bedroom Studio Family Friendly Creative Types Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Orange</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Modern Home Compact Studio Family Friendly Homeowners Practical Buyers Warm Textured Designed for Versatile Layout ...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Living Room Home Office Family Friendly Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Light</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Sleeper Convertible Corduroy Loveseat Sofa Couch for Cozy Cottage Compact Studio Family Friendly Traditional Families Practical Buyers Warm Textured Perfect for Warm In...</t>
+          <t>KEIKI 78" 2Seat Sleeper Corduroy Sofa Couch for Cozy Cottage Apartment Living Family Friendly Traditional Families Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Beige</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Executive Suite Family Living Room Family Friendly Luxury Buyers Adaptable Homeowners Warm Textured Ideal for Warm Textured Loungin...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Executive Suite Small Space Family Friendly Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Beach House Family Living Room Family Friendly Nautical Fans Adaptable Homeowners Warm Textured Great for Comfortable Gathering Spa...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Beach House Bedroom Studio Family Friendly Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Azure</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Coastal Home Family Living Room Family Friendly Beach Lovers Adaptable Homeowners Warm Textured Designed for Flexible Configuration...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Coastal Home Home Office Family Friendly Beach Lovers Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Blue</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Rustic Home Family Living Room Family Friendly Nature Lovers Adaptable Homeowners Warm Textured Perfect for Grounded Natural Relaxa...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Rustic Home Apartment Living Family Friendly Rustic Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Contemporary Design Brown</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Modern Home Family Living Room Family Friendly Homeowners Adaptable Homeowners Warm Textured Ideal for Warm Textured Lounging Rusti...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Zen Space Small Space Family Friendly Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Grayish Green</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Garden Oasis Family Living Room Family Friendly Plant Parents Adaptable Homeowners Warm Textured Great for Comfortable Gathering Sp...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Garden Home Bedroom Studio Family Friendly Nature Lovers Luxurious Elegant Sophisticated Refined Design Stylish Quality Design Green</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Artistic Studio Family Living Room Family Friendly Creative Types Adaptable Homeowners Warm Textured Designed for Flexible Configur...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Creative Studio Home Office Family Friendly Creative Types Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Orange</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Modern Home Family Living Room Family Friendly Homeowners Adaptable Homeowners Warm Textured Perfect for Comfortable Relaxation Rus...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Living Room Apartment Living Family Friendly Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Contemporary Design Light Gray</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Cozy Cottage Family Living Room Family Friendly Traditional Families Adaptable Homeowners Warm Textured Ideal for Warm Textured Lou...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Cozy Cottage Small Space Family Friendly Traditional Families Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Beige</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 106" 4Seat Modular Convertible Corduroy Sofa Couch for Industrial Loft Family Living Room Family Friendly Urban Professionals Adaptable Homeowners Warm Textured Great for Comfortable Gat...</t>
+          <t>KEIKI 106" 4Seat Modular Sectional Corduroy Sofa Couch for Urban Loft Bedroom Studio Family Friendly Urban Professionals Luxurious Elegant Sophisticated Refined Design Quality Design Black</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Convertible Turtle Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Comfort Seekers Urban Professionals Practical Buyers Ultra Soft Plush Designed for Vers...</t>
+          <t>KEIKI 78" 2Seat Turtle Velvet Sofa Couch for Urban Loft Home Office Comfort Seekers Urban Professionals Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Convertible Turtle Velvet Loveseat Sofa Couch for Bright Modern Home Compact Studio Comfort Seekers Minimalists Practical Buyers Ultra Soft Plush Perfect for Clean Airy...</t>
+          <t>KEIKI 78" 2Seat Turtle Velvet Sofa Couch for Modern Home Apartment Living Comfort Seekers Minimalists Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 78" 2Seat Modular Convertible Turtle Velvet Loveseat Sofa Couch for Executive Suite Compact Studio Comfort Seekers Luxury Buyers Practical Buyers Ultra Soft Plush Ideal for Ultra Soft Pl...</t>
+          <t>KEIKI 78" 2Seat Turtle Velvet Sofa Couch for Executive Suite Small Space Comfort Seekers Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Modern Home Compact Studio Comfort Seekers Homeowners Practical Buyers Ultra Soft Plush Great for Intimate Cozy Corner Contemporar...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch for City Apartment Bedroom Studio Comfort Seekers Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Gray</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Comfort Seekers Urban Professionals Practical Buyers Ultra Soft Plush Designed for Versatile Layout...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch for Urban Loft Home Office Comfort Seekers Urban Professionals Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Black</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Cozy Cottage Compact Studio Comfort Seekers Traditional Families Practical Buyers Ultra Soft Plush Perfect for Warm Inviting Relax...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch for Cozy Cottage Apartment Living Comfort Seekers Traditional Families Soft Plush Comfortable Cozy Relaxing Lounge Contemporary Design Beige</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Feminine Retreat Compact Studio Comfort Seekers Glam Seekers Practical Buyers Ultra Soft Plush Ideal for Ultra Soft Plush Lounging...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch for Feminine Retreat Small Space Comfort Seekers Glam Seekers Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Pink</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Rustic Home Compact Studio Comfort Seekers Nature Lovers Practical Buyers Ultra Soft Plush Great for Intimate Cozy Corner Contempo...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch for Rustic Home Bedroom Studio Comfort Seekers Rustic Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Brown</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Modern Home Compact Studio Comfort Seekers Homeowners Practical Buyers Ultra Soft Plush Designed for Versatile Layout Contemporary...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch for Living Room Home Office Comfort Seekers Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 56" 2Seat Modular Turtle Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Comfort Seekers Beach Lovers Practical Buyers Ultra Soft Plush Perfect for Serene Peaceful Relaxation ...</t>
+          <t>KEIKI 56" 2Seat Turtle Velvet Loveseat Sofa Couch for Coastal Home Apartment Living Comfort Seekers Beach Lovers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Blue</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Convertible Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Loungin...</t>
+          <t>KEIKI 76" 2Seat Velvet Sofa Couch for Coastal Home Small Space Style Conscious Beach Lovers Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Blue</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Convertible Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Practical Buyers Luxuriously Soft Great for Intimate Cozy Corner Gl...</t>
+          <t>KEIKI 76" 2Seat Velvet Sofa Couch for Garden Home Bedroom Studio Style Conscious Nature Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Convertible Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Designed for Versatile L...</t>
+          <t>KEIKI 76" 2Seat Velvet Sofa Couch for Urban Loft Home Office Style Conscious Urban Professionals Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Black</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Convertible Velvet Loveseat Sofa Couch for Cozy Cottage Compact Studio Style Conscious Traditional Families Practical Buyers Luxuriously Soft Perfect for Warm Inviting ...</t>
+          <t>KEIKI 76" 2Seat Velvet Sofa Couch for Cozy Cottage Apartment Living Style Conscious Traditional Families Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Beige</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Gray</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for City Apartment Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Gray</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Practical Buyers Luxuriously Soft Great for Intimate Cozy Corner Glam Modern Blue</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Coastal Home Bedroom Studio Style Conscious Beach Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality High Quality Premium Design Blue</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Designed for Versatile Layout Glam M...</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Urban Loft Home Office Style Conscious Urban Professionals Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Black</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Feminine Retreat Compact Studio Style Conscious Glam Seekers Practical Buyers Luxuriously Soft Perfect for Romantic Soft Relaxation Glam ...</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Feminine Retreat Apartment Living Style Conscious Glam Seekers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 72" 2Seat Modular Velvet Loveseat Sofa Couch for Cozy Cottage Compact Studio Style Conscious Traditional Families Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lounging Gl...</t>
+          <t>KEIKI 72" 2Seat Velvet Sofa Couch for Cozy Cottage Small Space Style Conscious Traditional Families Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Beige</t>
         </is>
       </c>
     </row>
